--- a/AAII_Financials/Yearly/IBEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>IBEX</t>
   </si>
@@ -656,152 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42186</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>644100</v>
+      </c>
+      <c r="E8" s="3">
         <v>558300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>508600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>523100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>492900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>443400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>405100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>368400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>342200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>334500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>323700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>455300</v>
+      </c>
+      <c r="E9" s="3">
         <v>385700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>356300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>375000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>374000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>335200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>293600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>282500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>34800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,42 +817,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E10" s="3">
         <v>172600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>152200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>148100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>118900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>108100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>85900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>299700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E15" s="3">
         <v>17200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>586800</v>
+      </c>
+      <c r="E17" s="3">
         <v>509700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>465900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>482600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>472200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>426300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>382400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>357900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>358900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>336900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>315100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E18" s="3">
         <v>48600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>42600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,8 +1213,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1201,213 +1234,228 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E21" s="3">
         <v>65800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>62100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>59500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>44200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4700</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E23" s="3">
         <v>45900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E26" s="3">
         <v>36900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E27" s="3">
         <v>36900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>33700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,14 +1670,14 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>15500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>4900</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,9 +1786,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1741,78 +1810,84 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E33" s="3">
         <v>36900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>33700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E35" s="3">
         <v>36900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>33700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42186</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E41" s="3">
         <v>15400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>62700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>57800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,20 +2141,20 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2078,54 +2167,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E43" s="3">
         <v>117200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>98600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>86400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>72600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>66900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>59800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>53500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>43300</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2153,8 +2248,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2168,99 +2263,108 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E46" s="3">
         <v>145600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>180000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>158600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>142400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>141400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>86000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>81800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>82000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>88600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>80700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2273,84 +2377,90 @@
       <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
-        <v>300</v>
+      <c r="G47" s="3">
+        <v>400</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
         <v>300</v>
       </c>
       <c r="J47" s="3">
+        <v>300</v>
+      </c>
+      <c r="K47" s="3">
         <v>200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5500</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E48" s="3">
         <v>94800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>89000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>112100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>106700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>84600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>82300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,44 +2468,47 @@
         <v>12200</v>
       </c>
       <c r="E49" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F49" s="3">
         <v>12500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>11800</v>
       </c>
       <c r="G49" s="3">
         <v>11800</v>
       </c>
       <c r="H49" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I49" s="3">
         <v>15000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>24600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E52" s="3">
         <v>12900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E54" s="3">
         <v>273200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>293900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>293300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>294200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>274300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>195200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>188300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>157100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>152200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>138400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E58" s="3">
         <v>15200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>28900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>39200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>52500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E59" s="3">
         <v>7500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E60" s="3">
         <v>79900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>105700</v>
       </c>
       <c r="I60" s="3">
         <v>105700</v>
       </c>
       <c r="J60" s="3">
+        <v>105700</v>
+      </c>
+      <c r="K60" s="3">
         <v>111400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>116200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>99900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>99400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>67200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E61" s="3">
         <v>54600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>76700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>73700</v>
-      </c>
-      <c r="I61" s="3">
-        <v>65800</v>
       </c>
       <c r="J61" s="3">
         <v>65800</v>
       </c>
       <c r="K61" s="3">
+        <v>65800</v>
+      </c>
+      <c r="L61" s="3">
         <v>9900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,9 +3215,12 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3071,44 +3228,47 @@
         <v>138900</v>
       </c>
       <c r="E66" s="3">
+        <v>138900</v>
+      </c>
+      <c r="F66" s="3">
         <v>128100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>143400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>180700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>193600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>179700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>129100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>123500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>122300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3246,11 +3413,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>20000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E72" s="3">
         <v>25700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-76400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-110700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-109500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-117200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-126100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-87500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-48100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-47200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E76" s="3">
         <v>134300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>165800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>150000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>113500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>80700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42186</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E81" s="3">
         <v>36900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>33700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E83" s="3">
         <v>17200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E89" s="3">
         <v>45700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>35900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9500</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4250,11 +4483,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,89 +4644,95 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-74700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>40900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-33900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -4492,52 +4740,58 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-47400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3600</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
